--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113413989</v>
+        <v>113412945</v>
       </c>
       <c r="B2" t="n">
         <v>56781</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,12 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosök</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426613</v>
+        <v>113426627</v>
       </c>
       <c r="B3" t="n">
-        <v>56781</v>
+        <v>94108</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,25 +800,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296209</v>
+        <v>296274</v>
       </c>
       <c r="R3" t="n">
-        <v>6530206</v>
+        <v>6530187</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,11 +864,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426618</v>
+        <v>113426609</v>
       </c>
       <c r="B4" t="n">
-        <v>56781</v>
+        <v>78713</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296302</v>
+        <v>296305</v>
       </c>
       <c r="R4" t="n">
-        <v>6530248</v>
+        <v>6530239</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,11 +966,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426623</v>
+        <v>113426618</v>
       </c>
       <c r="B5" t="n">
-        <v>96261</v>
+        <v>56781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,25 +1004,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1047,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296233</v>
+        <v>296302</v>
       </c>
       <c r="R5" t="n">
-        <v>6530173</v>
+        <v>6530248</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,6 +1068,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,7 +1102,7 @@
         <v>113426624</v>
       </c>
       <c r="B6" t="n">
-        <v>96261</v>
+        <v>96277</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426627</v>
+        <v>113426623</v>
       </c>
       <c r="B7" t="n">
-        <v>94092</v>
+        <v>96277</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,21 +1217,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296274</v>
+        <v>296233</v>
       </c>
       <c r="R7" t="n">
-        <v>6530187</v>
+        <v>6530173</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1313,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426609</v>
+        <v>113426613</v>
       </c>
       <c r="B8" t="n">
-        <v>78697</v>
+        <v>56781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,21 +1319,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1353,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296305</v>
+        <v>296209</v>
       </c>
       <c r="R8" t="n">
-        <v>6530239</v>
+        <v>6530206</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,6 +1379,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426624</v>
+        <v>113426613</v>
       </c>
       <c r="B6" t="n">
-        <v>96277</v>
+        <v>56781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296271</v>
+        <v>296209</v>
       </c>
       <c r="R6" t="n">
-        <v>6530251</v>
+        <v>6530206</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1175,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,7 +1206,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426623</v>
+        <v>113426624</v>
       </c>
       <c r="B7" t="n">
         <v>96277</v>
@@ -1241,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296233</v>
+        <v>296271</v>
       </c>
       <c r="R7" t="n">
-        <v>6530173</v>
+        <v>6530251</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1303,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426613</v>
+        <v>113426623</v>
       </c>
       <c r="B8" t="n">
-        <v>56781</v>
+        <v>96277</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1315,25 +1320,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1343,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296209</v>
+        <v>296233</v>
       </c>
       <c r="R8" t="n">
-        <v>6530206</v>
+        <v>6530173</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1379,11 +1384,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113412945</v>
+        <v>113413989</v>
       </c>
       <c r="B2" t="n">
         <v>56781</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -890,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426609</v>
+        <v>113426623</v>
       </c>
       <c r="B4" t="n">
-        <v>78713</v>
+        <v>96277</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -902,25 +907,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296305</v>
+        <v>296233</v>
       </c>
       <c r="R4" t="n">
-        <v>6530239</v>
+        <v>6530173</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -992,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426618</v>
+        <v>113426609</v>
       </c>
       <c r="B5" t="n">
-        <v>56781</v>
+        <v>78713</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296302</v>
+        <v>296305</v>
       </c>
       <c r="R5" t="n">
-        <v>6530248</v>
+        <v>6530239</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1068,11 +1073,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426613</v>
+        <v>113426618</v>
       </c>
       <c r="B6" t="n">
         <v>56781</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296209</v>
+        <v>296302</v>
       </c>
       <c r="R6" t="n">
-        <v>6530206</v>
+        <v>6530248</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426624</v>
+        <v>113426613</v>
       </c>
       <c r="B7" t="n">
-        <v>96277</v>
+        <v>56781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,25 +1218,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296271</v>
+        <v>296209</v>
       </c>
       <c r="R7" t="n">
-        <v>6530251</v>
+        <v>6530206</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1282,6 +1282,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,7 +1313,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426623</v>
+        <v>113426624</v>
       </c>
       <c r="B8" t="n">
         <v>96277</v>
@@ -1348,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296233</v>
+        <v>296271</v>
       </c>
       <c r="R8" t="n">
-        <v>6530173</v>
+        <v>6530251</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113413989</v>
+        <v>113412945</v>
       </c>
       <c r="B2" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,12 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosök</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426627</v>
+        <v>113426623</v>
       </c>
       <c r="B3" t="n">
-        <v>94108</v>
+        <v>96289</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296274</v>
+        <v>296233</v>
       </c>
       <c r="R3" t="n">
-        <v>6530187</v>
+        <v>6530173</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -895,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426623</v>
+        <v>113426609</v>
       </c>
       <c r="B4" t="n">
-        <v>96277</v>
+        <v>78725</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,25 +902,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296233</v>
+        <v>296305</v>
       </c>
       <c r="R4" t="n">
-        <v>6530173</v>
+        <v>6530239</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -997,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426609</v>
+        <v>113426627</v>
       </c>
       <c r="B5" t="n">
-        <v>78713</v>
+        <v>94120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,25 +1004,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296305</v>
+        <v>296274</v>
       </c>
       <c r="R5" t="n">
-        <v>6530239</v>
+        <v>6530187</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1099,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426618</v>
+        <v>113426613</v>
       </c>
       <c r="B6" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296302</v>
+        <v>296209</v>
       </c>
       <c r="R6" t="n">
-        <v>6530248</v>
+        <v>6530206</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1206,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426613</v>
+        <v>113426618</v>
       </c>
       <c r="B7" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296209</v>
+        <v>296302</v>
       </c>
       <c r="R7" t="n">
-        <v>6530206</v>
+        <v>6530248</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1316,7 +1311,7 @@
         <v>113426624</v>
       </c>
       <c r="B8" t="n">
-        <v>96277</v>
+        <v>96289</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426623</v>
+        <v>113426618</v>
       </c>
       <c r="B3" t="n">
-        <v>96289</v>
+        <v>56782</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,25 +800,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296233</v>
+        <v>296302</v>
       </c>
       <c r="R3" t="n">
-        <v>6530173</v>
+        <v>6530248</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -864,6 +864,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426609</v>
+        <v>113426613</v>
       </c>
       <c r="B4" t="n">
-        <v>78725</v>
+        <v>56782</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296305</v>
+        <v>296209</v>
       </c>
       <c r="R4" t="n">
-        <v>6530239</v>
+        <v>6530206</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,6 +971,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1094,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426613</v>
+        <v>113426623</v>
       </c>
       <c r="B6" t="n">
-        <v>56782</v>
+        <v>96289</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1106,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296209</v>
+        <v>296233</v>
       </c>
       <c r="R6" t="n">
-        <v>6530206</v>
+        <v>6530173</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1170,11 +1180,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426618</v>
+        <v>113426624</v>
       </c>
       <c r="B7" t="n">
-        <v>56782</v>
+        <v>96289</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1213,25 +1218,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296302</v>
+        <v>296271</v>
       </c>
       <c r="R7" t="n">
-        <v>6530248</v>
+        <v>6530251</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1277,11 +1282,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426624</v>
+        <v>113426609</v>
       </c>
       <c r="B8" t="n">
-        <v>96289</v>
+        <v>78725</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1320,25 +1320,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296271</v>
+        <v>296305</v>
       </c>
       <c r="R8" t="n">
-        <v>6530251</v>
+        <v>6530239</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426613</v>
+        <v>113426623</v>
       </c>
       <c r="B4" t="n">
-        <v>56782</v>
+        <v>96311</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,25 +907,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296209</v>
+        <v>296233</v>
       </c>
       <c r="R4" t="n">
-        <v>6530206</v>
+        <v>6530173</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,11 +971,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426627</v>
+        <v>113426613</v>
       </c>
       <c r="B5" t="n">
-        <v>94120</v>
+        <v>56782</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,25 +1009,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296274</v>
+        <v>296209</v>
       </c>
       <c r="R5" t="n">
-        <v>6530187</v>
+        <v>6530206</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1078,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426623</v>
+        <v>113426624</v>
       </c>
       <c r="B6" t="n">
-        <v>96289</v>
+        <v>96311</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296233</v>
+        <v>296271</v>
       </c>
       <c r="R6" t="n">
-        <v>6530173</v>
+        <v>6530251</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426624</v>
+        <v>113426609</v>
       </c>
       <c r="B7" t="n">
-        <v>96289</v>
+        <v>78747</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,25 +1218,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296271</v>
+        <v>296305</v>
       </c>
       <c r="R7" t="n">
-        <v>6530251</v>
+        <v>6530239</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1308,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426609</v>
+        <v>113426627</v>
       </c>
       <c r="B8" t="n">
-        <v>78725</v>
+        <v>94142</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1320,25 +1320,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296305</v>
+        <v>296274</v>
       </c>
       <c r="R8" t="n">
-        <v>6530239</v>
+        <v>6530187</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113412945</v>
+        <v>113413989</v>
       </c>
       <c r="B2" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426618</v>
+        <v>113426613</v>
       </c>
       <c r="B3" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296302</v>
+        <v>296209</v>
       </c>
       <c r="R3" t="n">
-        <v>6530248</v>
+        <v>6530206</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -895,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426623</v>
+        <v>113426627</v>
       </c>
       <c r="B4" t="n">
-        <v>96311</v>
+        <v>94146</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296233</v>
+        <v>296274</v>
       </c>
       <c r="R4" t="n">
-        <v>6530173</v>
+        <v>6530187</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -997,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426613</v>
+        <v>113426623</v>
       </c>
       <c r="B5" t="n">
-        <v>56782</v>
+        <v>96315</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,25 +1014,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296209</v>
+        <v>296233</v>
       </c>
       <c r="R5" t="n">
-        <v>6530206</v>
+        <v>6530173</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1073,11 +1078,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,7 +1107,7 @@
         <v>113426624</v>
       </c>
       <c r="B6" t="n">
-        <v>96311</v>
+        <v>96315</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>113426609</v>
       </c>
       <c r="B7" t="n">
-        <v>78747</v>
+        <v>78751</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1308,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426627</v>
+        <v>113426618</v>
       </c>
       <c r="B8" t="n">
-        <v>94142</v>
+        <v>56785</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1320,25 +1320,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296274</v>
+        <v>296302</v>
       </c>
       <c r="R8" t="n">
-        <v>6530187</v>
+        <v>6530248</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1384,6 +1384,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113413989</v>
+        <v>113412945</v>
       </c>
       <c r="B2" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,12 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosök</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426613</v>
+        <v>113426609</v>
       </c>
       <c r="B3" t="n">
-        <v>56785</v>
+        <v>78751</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296209</v>
+        <v>296305</v>
       </c>
       <c r="R3" t="n">
-        <v>6530206</v>
+        <v>6530239</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,11 +864,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426627</v>
+        <v>113426618</v>
       </c>
       <c r="B4" t="n">
-        <v>94146</v>
+        <v>56785</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,25 +902,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -940,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296274</v>
+        <v>296302</v>
       </c>
       <c r="R4" t="n">
-        <v>6530187</v>
+        <v>6530248</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,6 +966,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426623</v>
+        <v>113426627</v>
       </c>
       <c r="B5" t="n">
-        <v>96315</v>
+        <v>94146</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,21 +1013,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296233</v>
+        <v>296274</v>
       </c>
       <c r="R5" t="n">
-        <v>6530173</v>
+        <v>6530187</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1104,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426624</v>
+        <v>113426623</v>
       </c>
       <c r="B6" t="n">
         <v>96315</v>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296271</v>
+        <v>296233</v>
       </c>
       <c r="R6" t="n">
-        <v>6530251</v>
+        <v>6530173</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1206,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426609</v>
+        <v>113426624</v>
       </c>
       <c r="B7" t="n">
-        <v>78751</v>
+        <v>96315</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1218,25 +1213,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296305</v>
+        <v>296271</v>
       </c>
       <c r="R7" t="n">
-        <v>6530239</v>
+        <v>6530251</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1308,7 +1303,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426618</v>
+        <v>113426613</v>
       </c>
       <c r="B8" t="n">
         <v>56785</v>
@@ -1348,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296302</v>
+        <v>296209</v>
       </c>
       <c r="R8" t="n">
-        <v>6530248</v>
+        <v>6530206</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426609</v>
+        <v>113426624</v>
       </c>
       <c r="B3" t="n">
-        <v>78751</v>
+        <v>96321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,25 +800,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296305</v>
+        <v>296271</v>
       </c>
       <c r="R3" t="n">
-        <v>6530239</v>
+        <v>6530251</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426618</v>
+        <v>113426613</v>
       </c>
       <c r="B4" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296302</v>
+        <v>296209</v>
       </c>
       <c r="R4" t="n">
-        <v>6530248</v>
+        <v>6530206</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1000,7 +1000,7 @@
         <v>113426627</v>
       </c>
       <c r="B5" t="n">
-        <v>94146</v>
+        <v>94152</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>113426623</v>
       </c>
       <c r="B6" t="n">
-        <v>96315</v>
+        <v>96321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1201,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426624</v>
+        <v>113426609</v>
       </c>
       <c r="B7" t="n">
-        <v>96315</v>
+        <v>78757</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1213,25 +1213,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296271</v>
+        <v>296305</v>
       </c>
       <c r="R7" t="n">
-        <v>6530251</v>
+        <v>6530239</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1303,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426613</v>
+        <v>113426618</v>
       </c>
       <c r="B8" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296209</v>
+        <v>296302</v>
       </c>
       <c r="R8" t="n">
-        <v>6530206</v>
+        <v>6530248</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -788,10 +788,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426624</v>
+        <v>113426627</v>
       </c>
       <c r="B3" t="n">
-        <v>96321</v>
+        <v>94152</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,21 +804,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296271</v>
+        <v>296274</v>
       </c>
       <c r="R3" t="n">
-        <v>6530251</v>
+        <v>6530187</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -890,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426613</v>
+        <v>113426623</v>
       </c>
       <c r="B4" t="n">
-        <v>56789</v>
+        <v>96321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -902,25 +902,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296209</v>
+        <v>296233</v>
       </c>
       <c r="R4" t="n">
-        <v>6530206</v>
+        <v>6530173</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -966,11 +966,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426627</v>
+        <v>113426624</v>
       </c>
       <c r="B5" t="n">
-        <v>94152</v>
+        <v>96321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,21 +1008,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296274</v>
+        <v>296271</v>
       </c>
       <c r="R5" t="n">
-        <v>6530187</v>
+        <v>6530251</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1099,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426623</v>
+        <v>113426609</v>
       </c>
       <c r="B6" t="n">
-        <v>96321</v>
+        <v>78757</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1106,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296233</v>
+        <v>296305</v>
       </c>
       <c r="R6" t="n">
-        <v>6530173</v>
+        <v>6530239</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1201,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426609</v>
+        <v>113426613</v>
       </c>
       <c r="B7" t="n">
-        <v>78757</v>
+        <v>56789</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,21 +1212,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296305</v>
+        <v>296209</v>
       </c>
       <c r="R7" t="n">
-        <v>6530239</v>
+        <v>6530206</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1277,6 +1272,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113412945</v>
+        <v>113413989</v>
       </c>
       <c r="B2" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426627</v>
+        <v>113426618</v>
       </c>
       <c r="B3" t="n">
-        <v>94152</v>
+        <v>56796</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,25 +805,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296274</v>
+        <v>296302</v>
       </c>
       <c r="R3" t="n">
-        <v>6530187</v>
+        <v>6530248</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -864,6 +869,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +903,7 @@
         <v>113426623</v>
       </c>
       <c r="B4" t="n">
-        <v>96321</v>
+        <v>96328</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -992,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426624</v>
+        <v>113426627</v>
       </c>
       <c r="B5" t="n">
-        <v>96321</v>
+        <v>94159</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1032,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296271</v>
+        <v>296274</v>
       </c>
       <c r="R5" t="n">
-        <v>6530251</v>
+        <v>6530187</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1097,7 +1107,7 @@
         <v>113426609</v>
       </c>
       <c r="B6" t="n">
-        <v>78757</v>
+        <v>78764</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1196,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426613</v>
+        <v>113426624</v>
       </c>
       <c r="B7" t="n">
-        <v>56789</v>
+        <v>96328</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1208,25 +1218,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1236,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296209</v>
+        <v>296271</v>
       </c>
       <c r="R7" t="n">
-        <v>6530206</v>
+        <v>6530251</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1272,11 +1282,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426618</v>
+        <v>113426613</v>
       </c>
       <c r="B8" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296302</v>
+        <v>296209</v>
       </c>
       <c r="R8" t="n">
-        <v>6530248</v>
+        <v>6530206</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113413989</v>
       </c>
       <c r="B2" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>113426618</v>
       </c>
       <c r="B3" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>113426623</v>
       </c>
       <c r="B4" t="n">
-        <v>96328</v>
+        <v>96333</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426627</v>
+        <v>113426609</v>
       </c>
       <c r="B5" t="n">
-        <v>94159</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,25 +1014,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296274</v>
+        <v>296305</v>
       </c>
       <c r="R5" t="n">
-        <v>6530187</v>
+        <v>6530239</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426609</v>
+        <v>113426627</v>
       </c>
       <c r="B6" t="n">
-        <v>78764</v>
+        <v>94164</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296305</v>
+        <v>296274</v>
       </c>
       <c r="R6" t="n">
-        <v>6530239</v>
+        <v>6530187</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1209,7 +1209,7 @@
         <v>113426624</v>
       </c>
       <c r="B7" t="n">
-        <v>96328</v>
+        <v>96333</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>113426613</v>
       </c>
       <c r="B8" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113413989</v>
       </c>
       <c r="B2" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426618</v>
+        <v>113426613</v>
       </c>
       <c r="B3" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296302</v>
+        <v>296209</v>
       </c>
       <c r="R3" t="n">
-        <v>6530248</v>
+        <v>6530206</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -903,7 +903,7 @@
         <v>113426623</v>
       </c>
       <c r="B4" t="n">
-        <v>96333</v>
+        <v>96361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1002,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426609</v>
+        <v>113426624</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>96361</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,25 +1014,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296305</v>
+        <v>296271</v>
       </c>
       <c r="R5" t="n">
-        <v>6530239</v>
+        <v>6530251</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426627</v>
+        <v>113426609</v>
       </c>
       <c r="B6" t="n">
-        <v>94164</v>
+        <v>78794</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296274</v>
+        <v>296305</v>
       </c>
       <c r="R6" t="n">
-        <v>6530187</v>
+        <v>6530239</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426624</v>
+        <v>113426627</v>
       </c>
       <c r="B7" t="n">
-        <v>96333</v>
+        <v>94192</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,21 +1222,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296271</v>
+        <v>296274</v>
       </c>
       <c r="R7" t="n">
-        <v>6530251</v>
+        <v>6530187</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1308,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426613</v>
+        <v>113426618</v>
       </c>
       <c r="B8" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296209</v>
+        <v>296302</v>
       </c>
       <c r="R8" t="n">
-        <v>6530206</v>
+        <v>6530248</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113413989</v>
+        <v>113413535</v>
       </c>
       <c r="B2" t="n">
         <v>56826</v>
@@ -751,7 +751,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426609</v>
+        <v>113426618</v>
       </c>
       <c r="B6" t="n">
-        <v>78794</v>
+        <v>56826</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296305</v>
+        <v>296302</v>
       </c>
       <c r="R6" t="n">
-        <v>6530239</v>
+        <v>6530248</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1180,6 +1180,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426618</v>
+        <v>113426609</v>
       </c>
       <c r="B8" t="n">
-        <v>56826</v>
+        <v>78794</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,21 +1329,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296302</v>
+        <v>296305</v>
       </c>
       <c r="R8" t="n">
-        <v>6530248</v>
+        <v>6530239</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1384,11 +1389,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -793,10 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426613</v>
+        <v>113426627</v>
       </c>
       <c r="B3" t="n">
-        <v>56826</v>
+        <v>94196</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,25 +805,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296209</v>
+        <v>296274</v>
       </c>
       <c r="R3" t="n">
-        <v>6530206</v>
+        <v>6530187</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,11 +869,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +898,7 @@
         <v>113426623</v>
       </c>
       <c r="B4" t="n">
-        <v>96361</v>
+        <v>96365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1002,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426624</v>
+        <v>113426609</v>
       </c>
       <c r="B5" t="n">
-        <v>96361</v>
+        <v>78794</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,25 +1009,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1042,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296271</v>
+        <v>296305</v>
       </c>
       <c r="R5" t="n">
-        <v>6530251</v>
+        <v>6530239</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426618</v>
+        <v>113426624</v>
       </c>
       <c r="B6" t="n">
-        <v>56826</v>
+        <v>96365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296302</v>
+        <v>296271</v>
       </c>
       <c r="R6" t="n">
-        <v>6530248</v>
+        <v>6530251</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1180,11 +1175,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426627</v>
+        <v>113426618</v>
       </c>
       <c r="B7" t="n">
-        <v>94192</v>
+        <v>56826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,25 +1213,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296274</v>
+        <v>296302</v>
       </c>
       <c r="R7" t="n">
-        <v>6530187</v>
+        <v>6530248</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1287,6 +1277,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426609</v>
+        <v>113426613</v>
       </c>
       <c r="B8" t="n">
-        <v>78794</v>
+        <v>56826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,21 +1324,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1353,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296305</v>
+        <v>296209</v>
       </c>
       <c r="R8" t="n">
-        <v>6530239</v>
+        <v>6530206</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1389,6 +1384,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113412945</v>
+        <v>113426622</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norra Blötevattnet, Boh</t>
+          <t>Blötevattnet, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296271</v>
+        <v>296244</v>
       </c>
       <c r="R2" t="n">
-        <v>6530270</v>
+        <v>6530307</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,19 +743,14 @@
           <t>2023-11-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-11-26</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:26</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,49 +765,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Kuylenstierna</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Kuylenstierna</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426618</v>
+        <v>113426627</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -828,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296302</v>
+        <v>296274</v>
       </c>
       <c r="R3" t="n">
-        <v>6530248</v>
+        <v>6530187</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -864,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-11-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,15 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426624</v>
+        <v>113426628</v>
       </c>
       <c r="B4" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -935,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296271</v>
+        <v>296306</v>
       </c>
       <c r="R4" t="n">
-        <v>6530251</v>
+        <v>6530234</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -997,37 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426623</v>
+        <v>113426609</v>
       </c>
       <c r="B5" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296233</v>
+        <v>296305</v>
       </c>
       <c r="R5" t="n">
-        <v>6530173</v>
+        <v>6530239</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1099,19 +1068,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426613</v>
+        <v>113412945</v>
       </c>
       <c r="B6" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1133,19 +1097,20 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blötevattnet, Boh</t>
+          <t>Norra Blötevattnet, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296208</v>
+        <v>296271</v>
       </c>
       <c r="R6" t="n">
-        <v>6530206</v>
+        <v>6530270</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1172,14 +1137,19 @@
           <t>2023-11-26</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-26</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,27 +1164,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Maria Kuylenstierna</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Maria Kuylenstierna</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426627</v>
+        <v>113426613</v>
       </c>
       <c r="B7" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1222,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296274</v>
+        <v>296208</v>
       </c>
       <c r="R7" t="n">
-        <v>6530187</v>
+        <v>6530206</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1282,6 +1247,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,37 +1278,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113426609</v>
+        <v>113426618</v>
       </c>
       <c r="B8" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1313,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>296305</v>
+        <v>296302</v>
       </c>
       <c r="R8" t="n">
-        <v>6530239</v>
+        <v>6530248</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1386,6 +1351,11 @@
           <t>2023-11-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1407,6 +1377,200 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113426623</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Blötevattnet, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>296233</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6530173</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Naverstad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113426624</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Blötevattnet, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>296271</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6530251</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Naverstad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-11-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13943-2023 artfynd.xlsx
+++ b/artfynd/A 13943-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113426622</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113426627</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113426628</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113426609</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113412945</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1275,6 +1305,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113426613</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1377,6 +1412,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113426618</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1474,6 +1514,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113426623</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1571,8 +1616,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113426624</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>